--- a/www/ig/fhir/core/ValueSet-fr-core-vs-email-type.xlsx
+++ b/www/ig/fhir/core/ValueSet-fr-core-vs-email-type.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_R256-TypeMes" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/www/ig/fhir/core/ValueSet-fr-core-vs-email-type.xlsx
+++ b/www/ig/fhir/core/ValueSet-fr-core-vs-email-type.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include from TRE_R256-TypeMes" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/www/ig/fhir/core/ValueSet-fr-core-vs-email-type.xlsx
+++ b/www/ig/fhir/core/ValueSet-fr-core-vs-email-type.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE_R256-TypeMes" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
